--- a/stories/arbres/ATOM-EMO.LEX.010-01.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.010-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sara a planté des graines avec maman. C'est dans le jardin. Chaque matin, Sara arrose un peu. C'est un effort, chaque jour. Aujourd'hui, une petite pousse sort. Sara sent sa poitrine chaude. Elle se tient droite. Maman dit : tu peux être fier de ton effort. Sara dit : je suis fier de mon effort. Le frère Kenzo a aussi une pousse. Sara dit : la tienne est belle aussi. Papa vient voir les deux plants. Ils regardent ensemble. Être fier, c'est l'effort. On le dit. On laisse de la place à l'autre.</t>
+          <t>Sara a planté des graines avec maman. C'est dans le jardin. Chaque matin, Sara arrose un peu. C'est un effort, chaque jour. Aujourd'hui, une petite pousse sort. Sara sent sa poitrine chaude. Elle se tient droite. Tu peux être fier de ton effort. Je suis fier de mon effort. Le frère Kenzo a aussi une pousse. La tienne est belle aussi. Papa vient voir les deux plants. Ils regardent ensemble. Être fier, c'est l'effort. On le dit. On laisse de la place à l'autre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a planté des graines avec maman. C'est dans le jardin. Chaque matin, Sara arrose un peu. C'est un effort, chaque jour. Aujourd'hui, une petite pousse sort. Sara sent sa poitrine chaude. Elle se tient droite.
+maman|Tu peux être fier de ton effort.
+enfant-f|Je suis fier de mon effort.
+narrateur|Le frère Kenzo a aussi une pousse.
+enfant-f|La tienne est belle aussi. Papa vient voir les deux plants.
+narrateur|Ils regardent ensemble. Être fier, c'est l'effort. On le dit. On laisse de la place à l'autre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1491,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|La pousse de Sara est sortie. Que dit-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1664,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a nommé : fier. Elle parle de son effort. La pousse de Kenzo a sa place aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1827,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Sara pose l'arrosoir. Maman ferme le portillon.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1994,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2034,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.010-01.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.010-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 narrateur|Ils regardent ensemble. Être fier, c'est l'effort. On le dit. On laisse de la place à l'autre.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1498,6 +1504,7 @@
           <t>narrateur|La pousse de Sara est sortie. Que dit-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1676,7 @@
           <t>narrateur|Sara a nommé : fier. Elle parle de son effort. La pousse de Kenzo a sa place aussi.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1832,6 +1840,7 @@
           <t>narrateur|Sara pose l'arrosoir. Maman ferme le portillon.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1999,6 +2008,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2017,7 +2027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2051,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2242,6 +2266,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.010-01.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.010-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Être fier</t>
+          <t>Les deux pousses</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sarah arrose chaque matin. Une pousse sort. Elle dit qu'elle est fière de son effort. La pousse de Nino a sa place aussi.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sara a planté des graines avec maman. C'est dans le jardin. Chaque matin, Sara arrose un peu. C'est un effort, chaque jour. Aujourd'hui, une petite pousse sort. Sara sent sa poitrine chaude. Elle se tient droite. Tu peux être fier de ton effort. Je suis fier de mon effort. Le frère Kenzo a aussi une pousse. La tienne est belle aussi. Papa vient voir les deux plants. Ils regardent ensemble. Être fier, c'est l'effort. On le dit. On laisse de la place à l'autre.</t>
+          <t>Une goutte glisse sur le bord d'un pot. Le pot est en terre, un peu rugueux. La terre sent le matin, toute fraîche. Une coccinelle marche sur une feuille. L'arrosoir jaune goutte encore, tout doux. Le gravier est frais sous les pieds. Sarah, tu as vu la coccinelle ? Oui, maman. Elle est rouge. Elle a des points noirs, tout petits. Deux pots attendent près du bac. Dedans, de la terre noire, un peu humide. On a planté des graines, ensemble. Chaque matin, un peu d'eau. Tout doux. En ce moment, Sarah tient l'arrosoir. Elle arrose un tout petit peu. L'eau fait un cercle sombre. J'arrose chaque matin. C'est un effort, chaque jour. Tu as porté l'arrosoir jusqu'ici ? Oui, papa. Il est un peu lourd. Sarah se penche vers le pot. Une petite pousse verte sort. Elle est toute fine, toute droite. Une pousse ! Elle est sortie. Tu l'as soignée. Chaque matin. Sarah sent sa poitrine chaude. Elle se tient droite, près du pot. Je suis fière de mon effort. Tu peux être fière de ton effort. Fière, c'est content d'un effort. Ce n'est pas rabaisser l'autre. Nino est près de l'autre pot. Une pousse sort aussi, chez lui. La mienne est sortie aussi. La tienne est belle aussi. Les deux plants ont leur place. On laisse de la place à l'autre. Tu as dit : je suis fière. Bravo, Sarah. C'est du bon travail. Nino, tu as arrosé aussi ? Oui. Chaque matin, un peu. Toi aussi, tu as fait un effort. Je suis fier de mon effort. Les deux pousses sont belles. On les regarde ensemble ? Oui. Tout près des pots. Ils regardent les deux plants. Une feuille tremble un peu. La coccinelle est partie sur l'herbe. Être fier, c'est l'effort. On le dit. On laisse de la place. Mon effort. Chaque matin. Tu as arrosé. La pousse est là. L'arrosoir peut reposer, maintenant. L'arrosoir jaune reste près du bac. Le gravier fait un petit bruit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,15 +1324,69 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Sara a planté des graines avec maman. C'est dans le jardin. Chaque matin, Sara arrose un peu. C'est un effort, chaque jour. Aujourd'hui, une petite pousse sort. Sara sent sa poitrine chaude. Elle se tient droite.
-maman|Tu peux être fier de ton effort.
-enfant-f|Je suis fier de mon effort.
-narrateur|Le frère Kenzo a aussi une pousse.
-enfant-f|La tienne est belle aussi. Papa vient voir les deux plants.
-narrateur|Ils regardent ensemble. Être fier, c'est l'effort. On le dit. On laisse de la place à l'autre.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Une goutte glisse sur le bord d'un pot.
+narrateur|Le pot est en terre, un peu rugueux.
+narrateur|La terre sent le matin, toute fraîche.
+narrateur|Une coccinelle marche sur une feuille.
+narrateur|L'arrosoir jaune goutte encore, tout doux.
+narrateur|Le gravier est frais sous les pieds.
+maman|Sarah, tu as vu la coccinelle ?
+enfant-f|Oui, maman. Elle est rouge.
+papa|Elle a des points noirs, tout petits.
+narrateur|Deux pots attendent près du bac.
+narrateur|Dedans, de la terre noire, un peu humide.
+maman|On a planté des graines, ensemble.
+papa|Chaque matin, un peu d'eau. Tout doux.
+narrateur|En ce moment, Sarah tient l'arrosoir.
+narrateur|Elle arrose un tout petit peu.
+narrateur|L'eau fait un cercle sombre.
+enfant-f|J'arrose chaque matin.
+maman|C'est un effort, chaque jour.
+papa|Tu as porté l'arrosoir jusqu'ici ?
+enfant-f|Oui, papa. Il est un peu lourd.
+narrateur|Sarah se penche vers le pot.
+narrateur|Une petite pousse verte sort.
+narrateur|Elle est toute fine, toute droite.
+enfant-f|Une pousse ! Elle est sortie.
+maman|Tu l'as soignée. Chaque matin.
+narrateur|Sarah sent sa poitrine chaude.
+narrateur|Elle se tient droite, près du pot.
+enfant-f|Je suis fière de mon effort.
+maman|Tu peux être fière de ton effort.
+papa|Fière, c'est content d'un effort.
+maman|Ce n'est pas rabaisser l'autre.
+narrateur|Nino est près de l'autre pot.
+narrateur|Une pousse sort aussi, chez lui.
+enfant-m|La mienne est sortie aussi.
+enfant-f|La tienne est belle aussi.
+papa|Les deux plants ont leur place.
+maman|On laisse de la place à l'autre.
+papa|Tu as dit : je suis fière.
+maman|Bravo, Sarah. C'est du bon travail.
+papa|Nino, tu as arrosé aussi ?
+enfant-m|Oui. Chaque matin, un peu.
+maman|Toi aussi, tu as fait un effort.
+enfant-m|Je suis fier de mon effort.
+enfant-f|Les deux pousses sont belles.
+papa|On les regarde ensemble ?
+enfant-f|Oui. Tout près des pots.
+narrateur|Ils regardent les deux plants.
+narrateur|Une feuille tremble un peu.
+narrateur|La coccinelle est partie sur l'herbe.
+maman|Être fier, c'est l'effort.
+papa|On le dit. On laisse de la place.
+enfant-f|Mon effort. Chaque matin.
+maman|Tu as arrosé. La pousse est là.
+papa|L'arrosoir peut reposer, maintenant.
+narrateur|L'arrosoir jaune reste près du bac.
+narrateur|Le gravier fait un petit bruit.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>jardin,arrosoir</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1345,7 +1411,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>La pousse de Sara est sortie. Que dit-elle ?</t>
+          <t>La pousse de Sarah est sortie. Que dit-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1501,7 +1567,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|La pousse de Sara est sortie. Que dit-elle ?</t>
+          <t>narrateur|La pousse de Sarah est sortie.
+narrateur|Que dit-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1529,7 +1596,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sara a nommé : fier. Elle parle de son effort. La pousse de Kenzo a sa place aussi.</t>
+          <t>Sarah a nommé : fière. Elle parle de son effort. La pousse de Nino a sa place aussi. Je suis fière de mon effort. Oui. De ton effort, chaque matin. Bravo. C'est du bon travail. La mienne a sa place aussi. Oui. Elle est belle, Nino. On laisse de la place à l'autre. Tu veux encore regarder les plants ? Encore un peu. Tout près. Les deux pousses restent droites. La terre reste sombre, un peu humide.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1673,10 +1740,26 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sara a nommé : fier. Elle parle de son effort. La pousse de Kenzo a sa place aussi.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Sarah a nommé : fière.
+narrateur|Elle parle de son effort.
+narrateur|La pousse de Nino a sa place aussi.
+enfant-f|Je suis fière de mon effort.
+maman|Oui. De ton effort, chaque matin.
+papa|Bravo. C'est du bon travail.
+enfant-m|La mienne a sa place aussi.
+enfant-f|Oui. Elle est belle, Nino.
+maman|On laisse de la place à l'autre.
+papa|Tu veux encore regarder les plants ?
+enfant-f|Encore un peu. Tout près.
+narrateur|Les deux pousses restent droites.
+narrateur|La terre reste sombre, un peu humide.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>jardin</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1701,7 +1784,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sara pose l'arrosoir. Maman ferme le portillon.</t>
+          <t>Sarah pose l'arrosoir près du bac. On ferme le portillon, tout doux ? Oui, maman. Les deux plants restent au jardin. Demain, on arrose encore. Encore un petit effort, demain. Tu as dit le mot : fière. Fière de mon effort. Bravo, Sarah. Le portillon cliquette tout bas. Le gravier n'est plus frais. Les deux pots restent côte à côte.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1837,10 +1920,25 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Sara pose l'arrosoir. Maman ferme le portillon.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Sarah pose l'arrosoir près du bac.
+maman|On ferme le portillon, tout doux ?
+enfant-f|Oui, maman.
+papa|Les deux plants restent au jardin.
+enfant-m|Demain, on arrose encore.
+maman|Encore un petit effort, demain.
+papa|Tu as dit le mot : fière.
+enfant-f|Fière de mon effort.
+maman|Bravo, Sarah.
+narrateur|Le portillon cliquette tout bas.
+narrateur|Le gravier n'est plus frais.
+narrateur|Les deux pots restent côte à côte.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>jardin,portillon</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1865,7 +1963,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'étais fière de mon effort. Bravo. Tu as arrosé chaque matin. Les deux pousses ont leur place. L'arrosoir jaune reste près du bac. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2005,7 +2103,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'étais fière de mon effort.
+maman|Bravo. Tu as arrosé chaque matin.
+papa|Les deux pousses ont leur place.
+narrateur|L'arrosoir jaune reste près du bac.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2027,7 +2129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2065,6 +2167,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.010-01.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.010-01.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une goutte glisse sur le bord d'un pot. Le pot est en terre, un peu rugueux. La terre sent le matin, toute fraîche. Une coccinelle marche sur une feuille. L'arrosoir jaune goutte encore, tout doux. Le gravier est frais sous les pieds. Sarah, tu as vu la coccinelle ? Oui, maman. Elle est rouge. Elle a des points noirs, tout petits. Deux pots attendent près du bac. Dedans, de la terre noire, un peu humide. On a planté des graines, ensemble. Chaque matin, un peu d'eau. Tout doux. En ce moment, Sarah tient l'arrosoir. Elle arrose un tout petit peu. L'eau fait un cercle sombre. J'arrose chaque matin. C'est un effort, chaque jour. Tu as porté l'arrosoir jusqu'ici ? Oui, papa. Il est un peu lourd. Sarah se penche vers le pot. Une petite pousse verte sort. Elle est toute fine, toute droite. Une pousse ! Elle est sortie. Tu l'as soignée. Chaque matin. Sarah sent sa poitrine chaude. Elle se tient droite, près du pot. Je suis fière de mon effort. Tu peux être fière de ton effort. Fière, c'est content d'un effort. Ce n'est pas rabaisser l'autre. Nino est près de l'autre pot. Une pousse sort aussi, chez lui. La mienne est sortie aussi. La tienne est belle aussi. Les deux plants ont leur place. On laisse de la place à l'autre. Tu as dit : je suis fière. Bravo, Sarah. C'est du bon travail. Nino, tu as arrosé aussi ? Oui. Chaque matin, un peu. Toi aussi, tu as fait un effort. Je suis fier de mon effort. Les deux pousses sont belles. On les regarde ensemble ? Oui. Tout près des pots. Ils regardent les deux plants. Une feuille tremble un peu. La coccinelle est partie sur l'herbe. Être fier, c'est l'effort. On le dit. On laisse de la place. Mon effort. Chaque matin. Tu as arrosé. La pousse est là. L'arrosoir peut reposer, maintenant. L'arrosoir jaune reste près du bac. Le gravier fait un petit bruit.</t>
+          <t>Une goutte glisse sur le bord d'un pot. Le pot est en terre, un peu rugueux. La terre sent le matin, toute fraîche. Une coccinelle marche sur une feuille. L'arrosoir jaune goutte encore, tout doux. Le gravier est frais sous les pieds. Sarah, tu as vu la coccinelle ? Oui, maman. Elle est rouge. Elle a des points noirs, tout petits. Deux pots attendent près du bac. Dedans, de la terre noire, un peu humide. On a planté des graines, ensemble. Chaque matin, un peu d'eau. Tout doux. En ce moment, Sarah tient l'arrosoir. Elle arrose un tout petit peu. L'eau fait un cercle sombre. J'arrose chaque matin. C'est un effort, chaque jour. Tu as porté l'arrosoir jusqu'ici ? Oui, papa. Il est un peu lourd. Sarah se penche vers le pot. Une petite pousse verte sort. Elle est toute fine, toute droite. Une pousse ! Elle est sortie. Tu l'as soignée. Chaque matin. Sarah sent sa poitrine chaude. Elle se tient droite, près du pot. Je suis fière de mon effort. Tu peux être fière de ton effort. Fière, c'est content d'un effort. Ce n'est pas rabaisser l'autre. Nino est près de l'autre pot. Une pousse sort aussi, chez lui. La mienne est sortie aussi. La tienne est belle aussi. Les deux plants ont leur place. On laisse de la place à l'autre. Tu as dit : je suis fière. Nino, tu as arrosé aussi ? Oui. Chaque matin, un peu. Toi aussi, tu as fait un effort. Je suis fier de mon effort. Les deux pousses sont belles. On les regarde ensemble ? Oui. Tout près des pots. Ils regardent les deux plants. Une feuille tremble un peu. La coccinelle est partie sur l'herbe. Être fier, c'est l'effort. On le dit. On laisse de la place. Mon effort. Chaque matin. Tu as arrosé. La pousse est là. L'arrosoir peut reposer, maintenant. L'arrosoir jaune reste près du bac. Le gravier fait un petit bruit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sara a planté des graines avec maman. C'est dans le jardin. Chaque matin, Sara arrose un peu. C'est un effort, chaque jour. Aujourd'hui, une petite pousse sort. Sara sent sa poitrine chaude. Elle se tient droite. Maman dit : tu peux être &lt;emphasis level="moderate"&gt;fier&lt;/emphasis&gt; de ton effort. Sara dit : je suis fier de mon effort. Le frère Kenzo a aussi une pousse. Sara dit : la tienne est belle aussi. Papa vient voir les deux plants. Ils regardent ensemble. Être fier, c'est l'effort. On le dit. On laisse de la place à l'autre.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une goutte glisse sur le bord d'un pot. Le pot est en terre, un peu rugueux. La terre sent le matin, toute fraîche. Une coccinelle marche sur une feuille. L'arrosoir jaune goutte encore, tout doux. Le gravier est frais sous les pieds. Sarah, tu as vu la coccinelle ? Oui, maman. Elle est rouge. Elle a des points noirs, tout petits. Deux pots attendent près du bac. Dedans, de la terre noire, un peu humide. On a planté des graines, ensemble. Chaque matin, un peu d'eau. Tout doux. En ce moment, Sarah tient l'arrosoir. Elle arrose un tout petit peu. L'eau fait un cercle sombre. J'arrose chaque matin. C'est un effort, chaque jour. Tu as porté l'arrosoir jusqu'ici ? Oui, papa. Il est un peu lourd. Sarah se penche vers le pot. Une petite pousse verte sort. Elle est toute fine, toute droite. Une pousse ! Elle est sortie. Tu l'as soignée. Chaque matin. Sarah sent sa poitrine chaude. Elle se tient droite, près du pot. Je suis fière de mon effort. Tu peux être fière de ton effort. Fière, c'est content d'un effort. Ce n'est pas rabaisser l'autre. Nino est près de l'autre pot. Une pousse sort aussi, chez lui. La mienne est sortie aussi. La tienne est belle aussi. Les deux plants ont leur place. On laisse de la place à l'autre. Tu as dit : je suis fière. Nino, tu as arrosé aussi ? Oui. Chaque matin, un peu. Toi aussi, tu as fait un effort. Je suis fier de mon effort. Les deux pousses sont belles. On les regarde ensemble ? Oui. Tout près des pots. Ils regardent les deux plants. Une feuille tremble un peu. La coccinelle est partie sur l'herbe. Être fier, c'est l'effort. On le dit. On laisse de la place. Mon effort. Chaque matin. Tu as arrosé. La pousse est là. L'arrosoir peut reposer, maintenant. L'arrosoir jaune reste près du bac. Le gravier fait un petit bruit.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1362,7 +1362,6 @@
 papa|Les deux plants ont leur place.
 maman|On laisse de la place à l'autre.
 papa|Tu as dit : je suis fière.
-maman|Bravo, Sarah. C'est du bon travail.
 papa|Nino, tu as arrosé aussi ?
 enfant-m|Oui. Chaque matin, un peu.
 maman|Toi aussi, tu as fait un effort.
@@ -1416,7 +1415,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;La pousse de Sara est sortie. Que dit-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>La pousse de Sarah est sortie. Que dit-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1571,7 +1570,6 @@
 narrateur|Que dit-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1596,12 +1594,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a nommé : fière. Elle parle de son effort. La pousse de Nino a sa place aussi. Je suis fière de mon effort. Oui. De ton effort, chaque matin. Bravo. C'est du bon travail. La mienne a sa place aussi. Oui. Elle est belle, Nino. On laisse de la place à l'autre. Tu veux encore regarder les plants ? Encore un peu. Tout près. Les deux pousses restent droites. La terre reste sombre, un peu humide.</t>
+          <t>Sarah a nommé : fière. Elle parle de son effort. La pousse de Nino a sa place aussi. Je suis fière de mon effort. Oui. De ton effort, chaque matin. La mienne a sa place aussi. Oui. Elle est belle, Nino. On laisse de la place à l'autre. Tu veux encore regarder les plants ? Encore un peu. Tout près. Les deux pousses restent droites. La terre reste sombre, un peu humide.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sara a nommé : &lt;emphasis level="moderate"&gt;fier&lt;/emphasis&gt;. Elle parle de son effort. La pousse de Kenzo a sa place aussi.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a nommé : fière. Elle parle de son effort. La pousse de Nino a sa place aussi. Je suis fière de mon effort. Oui. De ton effort, chaque matin. La mienne a sa place aussi. Oui. Elle est belle, Nino. On laisse de la place à l'autre. Tu veux encore regarder les plants ? Encore un peu. Tout près. Les deux pousses restent droites. La terre reste sombre, un peu humide.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1745,7 +1743,6 @@
 narrateur|La pousse de Nino a sa place aussi.
 enfant-f|Je suis fière de mon effort.
 maman|Oui. De ton effort, chaque matin.
-papa|Bravo. C'est du bon travail.
 enfant-m|La mienne a sa place aussi.
 enfant-f|Oui. Elle est belle, Nino.
 maman|On laisse de la place à l'autre.
@@ -1789,7 +1786,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sara pose l'arrosoir. Maman ferme le portillon.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah pose l'arrosoir près du bac. On ferme le portillon, tout doux ? Oui, maman. Les deux plants restent au jardin. Demain, on arrose encore. Encore un petit effort, demain. Tu as dit le mot : fière. Fière de mon effort. Bravo, Sarah. Le portillon cliquette tout bas. Le gravier n'est plus frais. Les deux pots restent côte à côte.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1963,12 +1960,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'étais fière de mon effort. Bravo. Tu as arrosé chaque matin. Les deux pousses ont leur place. L'arrosoir jaune reste près du bac. L'histoire est finie.</t>
+          <t>J'étais fière de mon effort. Bravo. Tu as arrosé chaque matin. Les deux pousses ont leur place. L'arrosoir jaune reste près du bac.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'étais fière de mon effort. Bravo. Tu as arrosé chaque matin. Les deux pousses ont leur place. L'arrosoir jaune reste près du bac.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2106,11 +2103,9 @@
           <t>enfant-f|J'étais fière de mon effort.
 maman|Bravo. Tu as arrosé chaque matin.
 papa|Les deux pousses ont leur place.
-narrateur|L'arrosoir jaune reste près du bac.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|L'arrosoir jaune reste près du bac.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2129,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2174,6 +2169,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.010-01.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.010-01.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sara, Kenzo, maman, papa</t>
+          <t>Sarah, Nino, maman, papa</t>
         </is>
       </c>
     </row>
